--- a/testcases/locations/location-legal.xlsx
+++ b/testcases/locations/location-legal.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2823,12 +2823,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TC-LOC-LGL-015</t>
+          <t xml:space="preserve">TC-LOC-LGL-015</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Country change resets both Legal dropdowns</t>
+          <t>Combined SC + T&amp;C change saves and persists both</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2847,11 +2847,10 @@
 Location: test office 1604
 Application: Navigator
 Sample input 1: "Legal"
-Sample input 2: "Country"
-Sample input 3: "United States"
-Sample input 4: "Canada"
-Sample input 5: "Service Charge Name"
-Sample input 6: "Terms and Conditions Name"</t>
+Sample input 2: "Service Charge Name"
+Sample input 3: "Administrative Fee"
+Sample input 4: "Terms and Conditions Name"
+Sample input 5: "Encore Terms and Conditions"</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2866,10 +2865,14 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Pending Automation</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>Office 1604 is open in Navigator. Legal tab is active</t>
@@ -2877,19 +2880,15 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1. Navigate to "Legal" tab</t>
+          <t>1. Reload page and navigate to "Legal" tab (clean form state before save cycle)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>The Legal tab is displayed with Service Charge Name showing "Resort Service Charge" and Terms and Conditions Name showing "LDW".</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>Not yet automated — pending coverage of the left-panel Country selector</t>
-        </is>
-      </c>
+          <t>The page reloads and the Legal tab is displayed in a clean state with the Save button disabled.</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
@@ -2904,12 +2903,12 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2. In left panel, change "Country" dropdown from "United States" to another value (e.g., "Canada")</t>
+          <t>2. Change "Service Charge Name" to "Administrative Fee"</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>The Country field updates to the new value.</t>
+          <t>The Service Charge Name field updates to display "Administrative Fee".</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -2927,12 +2926,12 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>3. Click "Legal" tab</t>
+          <t>3. Change "Terms and Conditions Name" to "Encore Terms and Conditions"</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>The Legal tab reloads and displays the updated Legal grid.</t>
+          <t>The Terms and Conditions Name field updates to display "Encore Terms and Conditions".</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -2950,12 +2949,12 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>4. Verify "Service Charge Name"</t>
+          <t>4. Verify left-panel "Save" button</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>The Service Charge Name field no longer shows "Resort Service Charge"; it has been reset.</t>
+          <t>The left-panel Save button is enabled.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -2973,86 +2972,38 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>5. Verify "Terms and Conditions Name"</t>
+          <t>5. Click left-panel "Save" button</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>The Terms and Conditions Name field no longer shows "LDW"; it has been reset.</t>
+          <t>The Save Changes confirmation dialog is displayed.</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>TC-LOC-LGL-016</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Verify Service Charge dropdown options are sorted alphabetically</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>legal</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Legal"
-Sample input 2: "Service Charge Name"</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Pending Automation</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Office 1604 is open in Navigator. Legal tab is active</t>
-        </is>
-      </c>
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1. Navigate to "Legal" tab</t>
+          <t>6. Click "Ok" in dialog</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>The Legal tab is displayed with the Legal panel visible.</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>Blocked — the Service Charge dropdown options are not sorted alphabetically, so the test would fail against current behavior. Pending an application fix</t>
-        </is>
-      </c>
+          <t>The dialog closes and both changes are saved.</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
@@ -3067,12 +3018,12 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2. Click "Service Charge Name" dropdown</t>
+          <t>7. Verify left-panel "Save" button</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>The Service Charge Name dropdown opens and displays the list of options.</t>
+          <t>The left-panel Save button is disabled.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -3090,12 +3041,12 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>3. Read all option texts</t>
+          <t>8. Reload page and navigate to "Legal" tab</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>All option texts in the dropdown are visible and legible.</t>
+          <t>The page reloads and the Legal tab is displayed with freshly loaded values.</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -3113,106 +3064,105 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>4. Compare to case-insensitive alphabetical sort</t>
+          <t>9. Verify "Service Charge Name"</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>The options are in alphabetical order.</t>
+          <t>The Service Charge Name field shows "Administrative Fee".</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>TC-LOC-LGL-017</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Verify Terms and Conditions dropdown options are sorted alphabetically</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>10. Verify "Terms and Conditions Name"</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions Name field shows "Encore Terms and Conditions".</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-LGL-016</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Verify an out-of-list Service Charge value cannot be submitted</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
         <is>
           <t>locations</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>legal</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
-Sample input 1: "Legal"
-Sample input 2: "Terms and Conditions Name"</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
+Sample input 1: "Service Charge"
+Sample input 2: "Administrative Fee"
+Sample input 3: "Legal"
+Sample input 4: "Resort Service Charge"
+Sample input 5: "LDW"</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Pending Automation</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
         <is>
           <t>Office 1604 is open in Navigator. Legal tab is active</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>1. Navigate to "Legal" tab</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>The Legal tab is displayed with the Legal panel visible.</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>Blocked — the Terms and Conditions dropdown options are not sorted alphabetically. Pending an application fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2. Click "Terms and Conditions Name" dropdown</t>
+          <t>1. Open the "Service Charge" dropdown and confirm an invalid, out-of-list value is NOT among the available options, while the current default value AND a valid alternate value ("Administrative Fee") ARE both present</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>The Terms and Conditions Name dropdown opens and displays the list of options.</t>
+          <t>The dropdown list excludes the invalid value and includes both "Resort Service Charge" and "Administrative Fee".</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -3230,12 +3180,12 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>3. Read all option texts</t>
+          <t>2. Reset the Legal row to its default Service Charge and Terms &amp; Conditions values</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>All option texts in the dropdown are visible and legible.</t>
+          <t>The Service Charge Name and Terms and Conditions Name fields display their default values, "Resort Service Charge" and "LDW".</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -3253,82 +3203,35 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>4. Compare to case-insensitive alphabetical sort</t>
+          <t>3. Select the valid alternate Service Charge ("Administrative Fee") from the dropdown</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>The options are in alphabetical order.</t>
+          <t>The Service Charge Name field updates to display "Administrative Fee".</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>TC-LOC-LGL-018</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Combined SC + T&amp;C change saves and persists both</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>legal</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Legal"
-Sample input 2: "Service Charge Name"
-Sample input 3: "Administrative Fee"
-Sample input 4: "Terms and Conditions Name"
-Sample input 5: "Encore Terms and Conditions"</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Office 1604 is open in Navigator. Legal tab is active</t>
-        </is>
-      </c>
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>1. Reload page and navigate to "Legal" tab (clean form state before save cycle)</t>
+          <t>4. Confirm the "Save" button becomes enabled and the dropdown now reads "Administrative Fee"</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>The page reloads and the Legal tab is displayed in a clean state with the Save button disabled.</t>
+          <t>The Save button is enabled and the dropdown displays "Administrative Fee".</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -3346,12 +3249,12 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2. Change "Service Charge Name" to "Administrative Fee"</t>
+          <t>5. Click "Save" and confirm the Save Changes dialog</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>The Service Charge Name field updates to display "Administrative Fee".</t>
+          <t>The Save Changes dialog is confirmed and the change is saved.</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -3369,12 +3272,12 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>3. Change "Terms and Conditions Name" to "Encore Terms and Conditions"</t>
+          <t>6. Confirm the "Save" button returns to disabled after the save completes</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>The Terms and Conditions Name field updates to display "Encore Terms and Conditions".</t>
+          <t>The Save button is disabled after the save completes.</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -3392,12 +3295,12 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>4. Verify left-panel "Save" button</t>
+          <t>7. Reload the page and return to the "Legal" tab</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>The left-panel Save button is enabled.</t>
+          <t>The page reloads and the Legal tab is displayed with the Legal panel visible.</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -3415,12 +3318,12 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>5. Click left-panel "Save" button</t>
+          <t>8. Confirm the persisted Service Charge value is "Administrative Fee" and is never the invalid value (end-to-end check at the server)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>The Save Changes confirmation dialog is displayed.</t>
+          <t>The persisted Service Charge value is "Administrative Fee", and the invalid value is absent server-side.</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -3438,393 +3341,47 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>6. Click "Ok" in dialog</t>
+          <t>9. Restore the Legal row to its default values ("Resort Service Charge" and "LDW")</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>The dialog closes and both changes are saved.</t>
+          <t>All checks pass. No UI path exposes an out-of-list value to the user, and a normal save persists only the valid selected value (never the invalid value) at the server</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>7. Verify left-panel "Save" button</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>The left-panel Save button is disabled.</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr"/>
-    </row>
+    <row r="93"/>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>8. Reload page and navigate to "Legal" tab</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>The page reloads and the Legal tab is displayed with freshly loaded values.</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>9. Verify "Service Charge Name"</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>The Service Charge Name field shows "Administrative Fee".</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>10. Verify "Terms and Conditions Name"</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions Name field shows "Encore Terms and Conditions".</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>TC-LOC-LGL-019</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Verify an out-of-list Service Charge value cannot be submitted</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>legal</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Service Charge"
-Sample input 2: "Administrative Fee"
-Sample input 3: "Legal"
-Sample input 4: "Resort Service Charge"
-Sample input 5: "LDW"</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Office 1604 is open in Navigator. Legal tab is active</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>1. Open the "Service Charge" dropdown and confirm an invalid, out-of-list value is NOT among the available options, while the current default value AND a valid alternate value ("Administrative Fee") ARE both present</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>The dropdown list excludes the invalid value and includes both "Resort Service Charge" and "Administrative Fee".</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>2. Reset the Legal row to its default Service Charge and Terms &amp; Conditions values</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>The Service Charge Name and Terms and Conditions Name fields display their default values, "Resort Service Charge" and "LDW".</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr"/>
-      <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>3. Select the valid alternate Service Charge ("Administrative Fee") from the dropdown</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>The Service Charge Name field updates to display "Administrative Fee".</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>4. Confirm the "Save" button becomes enabled and the dropdown now reads "Administrative Fee"</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>The Save button is enabled and the dropdown displays "Administrative Fee".</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr"/>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>5. Click "Save" and confirm the Save Changes dialog</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>The Save Changes dialog is confirmed and the change is saved.</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>6. Confirm the "Save" button returns to disabled after the save completes</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>The Save button is disabled after the save completes.</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr"/>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>7. Reload the page and return to the "Legal" tab</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>The page reloads and the Legal tab is displayed with the Legal panel visible.</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>8. Confirm the persisted Service Charge value is "Administrative Fee" and is never the invalid value (end-to-end check at the server)</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>The persisted Service Charge value is "Administrative Fee", and the invalid value is absent server-side.</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr"/>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>9. Restore the Legal row to its default values ("Resort Service Charge" and "LDW")</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>All checks pass. No UI path exposes an out-of-list value to the user, and a normal save persists only the valid selected value (never the invalid value) at the server</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr"/>
-    </row>
-    <row r="106"/>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Location — Legal</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr"/>
-      <c r="D107" s="2" t="inlineStr"/>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>Automated: 16 / Pending: 3</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>Pass:16 Fail:0 Skipped:0 Blocked:2</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr"/>
-      <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="inlineStr"/>
-      <c r="M107" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr"/>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automated: 16 / Pending: 0</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass:16 Fail:0 Skipped:0 Blocked:0</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
         <is>
           <t>Last Updated: 2026-08-12</t>
         </is>
